--- a/data/trans_dic/P57GLOBAL_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,15; 78,38</t>
+          <t>73,29; 78,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,74; 75,45</t>
+          <t>69,68; 75,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,11; 84,6</t>
+          <t>78,76; 84,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,1; 71,31</t>
+          <t>62,74; 71,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,85; 81,47</t>
+          <t>76,8; 81,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,18; 79,72</t>
+          <t>75,11; 79,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,5; 89,9</t>
+          <t>85,36; 89,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,74; 73,79</t>
+          <t>68,7; 73,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,04; 79,38</t>
+          <t>76,02; 79,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,65; 77,21</t>
+          <t>73,39; 77,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83,51; 86,92</t>
+          <t>83,54; 87,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,2; 71,87</t>
+          <t>67,43; 71,66</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,43; 70,05</t>
+          <t>65,34; 70,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,04; 69,38</t>
+          <t>64,85; 69,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,6; 84,87</t>
+          <t>81,66; 84,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,4; 63,22</t>
+          <t>38,29; 63,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,59; 71,13</t>
+          <t>66,34; 70,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,5; 77,68</t>
+          <t>73,51; 77,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,15; 87,33</t>
+          <t>84,07; 87,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,27; 64,59</t>
+          <t>54,27; 64,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,65; 70,08</t>
+          <t>66,64; 69,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,65; 72,73</t>
+          <t>69,6; 72,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,38; 85,59</t>
+          <t>83,25; 85,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,42; 62,76</t>
+          <t>45,89; 62,95</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,27; 72,58</t>
+          <t>64,18; 72,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,37; 72,44</t>
+          <t>62,49; 71,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,53; 80,26</t>
+          <t>72,67; 80,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,13; 65,49</t>
+          <t>56,3; 64,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,13; 69,0</t>
+          <t>59,87; 68,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,78; 72,15</t>
+          <t>62,82; 71,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,13; 79,19</t>
+          <t>71,65; 79,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,44; 59,88</t>
+          <t>53,48; 60,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,65; 69,74</t>
+          <t>63,78; 69,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,07; 70,58</t>
+          <t>64,31; 70,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,74; 78,92</t>
+          <t>73,31; 78,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,38; 61,67</t>
+          <t>56,1; 61,62</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,81; 71,98</t>
+          <t>68,8; 72,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,18; 70,62</t>
+          <t>67,18; 70,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,58; 83,1</t>
+          <t>80,49; 83,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,93; 63,6</t>
+          <t>42,9; 63,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,65; 73,61</t>
+          <t>70,66; 73,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,73; 76,86</t>
+          <t>73,75; 76,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,54; 85,98</t>
+          <t>83,44; 85,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,57; 64,53</t>
+          <t>57,3; 64,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,14; 72,39</t>
+          <t>70,2; 72,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,93; 73,2</t>
+          <t>71,04; 73,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82,42; 84,28</t>
+          <t>82,39; 84,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,37; 63,3</t>
+          <t>53,09; 63,49</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>754743; 808685</t>
+          <t>756153; 809719</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>666077; 720661</t>
+          <t>665493; 722463</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>592137; 633259</t>
+          <t>589557; 631700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>317139; 358399</t>
+          <t>315299; 358166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1010710; 1071449</t>
+          <t>1010053; 1066981</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>993434; 1053395</t>
+          <t>992488; 1051148</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>843124; 886539</t>
+          <t>841709; 887033</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>501582; 538400</t>
+          <t>501234; 539567</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1784508; 1862817</t>
+          <t>1784014; 1861300</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1676724; 1757728</t>
+          <t>1670823; 1758628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1448641; 1507697</t>
+          <t>1449065; 1509815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>828092; 885582</t>
+          <t>830907; 883013</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1106968; 1185109</t>
+          <t>1105325; 1186205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1266977; 1351536</t>
+          <t>1263295; 1346422</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1679815; 1747256</t>
+          <t>1681050; 1748070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>825443; 1433521</t>
+          <t>868268; 1441505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1055130; 1127025</t>
+          <t>1051256; 1123655</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1282770; 1355666</t>
+          <t>1282843; 1355890</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1658025; 1720697</t>
+          <t>1656559; 1717600</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1066341; 1292967</t>
+          <t>1086380; 1295955</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2183673; 2296095</t>
+          <t>2183172; 2290593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2572359; 2686096</t>
+          <t>2570398; 2684162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3359276; 3448303</t>
+          <t>3354214; 3448794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1981796; 2679279</t>
+          <t>1959305; 2687620</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>351595; 397041</t>
+          <t>351067; 396001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301758; 344967</t>
+          <t>297588; 340311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>394587; 436677</t>
+          <t>395341; 437077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>362056; 415032</t>
+          <t>356766; 410580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>286456; 328722</t>
+          <t>285240; 327157</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>283888; 326283</t>
+          <t>284078; 324293</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>389387; 427495</t>
+          <t>386826; 426866</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>350199; 392358</t>
+          <t>350477; 394719</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651417; 713696</t>
+          <t>652789; 714166</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>594851; 655264</t>
+          <t>597037; 658482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>799271; 855456</t>
+          <t>794588; 851957</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>726703; 794880</t>
+          <t>723192; 794249</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2250542; 2354164</t>
+          <t>2250039; 2355032</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2270100; 2386346</t>
+          <t>2270364; 2376428</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2700372; 2785047</t>
+          <t>2697468; 2789583</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1461251; 2164884</t>
+          <t>1460127; 2166149</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2385333; 2485211</t>
+          <t>2385562; 2491086</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2594601; 2704541</t>
+          <t>2595216; 2702607</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2920744; 3006130</t>
+          <t>2917427; 3003380</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1949602; 2185378</t>
+          <t>1940528; 2193395</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4661791; 4811229</t>
+          <t>4665905; 4815066</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4893206; 5049398</t>
+          <t>4900532; 5052851</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5643807; 5771006</t>
+          <t>5641527; 5767447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3488230; 4298245</t>
+          <t>3604878; 4311230</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57GLOBAL_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,29; 78,48</t>
+          <t>72,82; 78,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,68; 75,64</t>
+          <t>69,6; 75,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,76; 84,39</t>
+          <t>79,14; 84,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,74; 71,27</t>
+          <t>63,36; 71,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,8; 81,13</t>
+          <t>77,07; 81,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,11; 79,55</t>
+          <t>74,99; 79,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,36; 89,95</t>
+          <t>85,62; 89,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,7; 73,95</t>
+          <t>69,76; 74,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,02; 79,31</t>
+          <t>76,07; 79,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,39; 77,25</t>
+          <t>73,5; 77,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83,54; 87,04</t>
+          <t>83,61; 87,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,43; 71,66</t>
+          <t>68,04; 72,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,34; 70,12</t>
+          <t>65,36; 69,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64,85; 69,12</t>
+          <t>65,02; 69,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,66; 84,91</t>
+          <t>81,53; 84,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,29; 63,57</t>
+          <t>61,78; 66,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,34; 70,91</t>
+          <t>66,41; 71,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,51; 77,69</t>
+          <t>73,54; 77,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,07; 87,17</t>
+          <t>84,25; 87,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,27; 64,74</t>
+          <t>63,33; 67,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,64; 69,91</t>
+          <t>66,67; 69,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,6; 72,68</t>
+          <t>69,53; 72,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,25; 85,6</t>
+          <t>83,26; 85,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,89; 62,95</t>
+          <t>63,18; 66,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,18; 72,39</t>
+          <t>64,62; 72,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,49; 71,46</t>
+          <t>62,92; 72,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,67; 80,34</t>
+          <t>72,66; 80,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,3; 64,79</t>
+          <t>57,85; 65,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,87; 68,67</t>
+          <t>60,0; 68,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,82; 71,71</t>
+          <t>62,66; 72,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,65; 79,07</t>
+          <t>71,92; 79,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,48; 60,24</t>
+          <t>54,56; 61,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,78; 69,78</t>
+          <t>63,69; 69,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,31; 70,92</t>
+          <t>64,21; 70,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,31; 78,6</t>
+          <t>73,73; 78,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,1; 61,62</t>
+          <t>57,04; 62,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,8; 72,01</t>
+          <t>68,69; 71,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,18; 70,32</t>
+          <t>67,18; 70,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,49; 83,24</t>
+          <t>80,57; 83,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,9; 63,64</t>
+          <t>62,32; 66,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,66; 73,79</t>
+          <t>70,83; 73,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,75; 76,8</t>
+          <t>73,72; 76,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,44; 85,9</t>
+          <t>83,53; 85,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,3; 64,77</t>
+          <t>63,77; 66,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,2; 72,44</t>
+          <t>70,27; 72,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,04; 73,25</t>
+          <t>71,08; 73,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82,39; 84,23</t>
+          <t>82,36; 84,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,09; 63,49</t>
+          <t>63,65; 66,04</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337137</t>
+          <t>382152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>520029</t>
+          <t>573544</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>857166</t>
+          <t>955696</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>756153; 809719</t>
+          <t>751281; 808253</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>665493; 722463</t>
+          <t>664724; 722912</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>589557; 631700</t>
+          <t>592350; 633970</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>315299; 358166</t>
+          <t>358399; 405179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1010053; 1066981</t>
+          <t>1013499; 1071707</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>992488; 1051148</t>
+          <t>990917; 1053627</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>841709; 887033</t>
+          <t>844338; 884078</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>501234; 539567</t>
+          <t>553571; 591168</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1784014; 1861300</t>
+          <t>1785190; 1865522</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1670823; 1758628</t>
+          <t>1673276; 1755263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1449065; 1509815</t>
+          <t>1450387; 1510012</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>830907; 883013</t>
+          <t>924818; 982842</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1267954</t>
+          <t>1416484</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1225904</t>
+          <t>1396466</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2493858</t>
+          <t>2812950</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1105325; 1186205</t>
+          <t>1105684; 1184045</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1263295; 1346422</t>
+          <t>1266595; 1350020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1681050; 1748070</t>
+          <t>1678483; 1747027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>868268; 1441505</t>
+          <t>1362894; 1470397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1051256; 1123655</t>
+          <t>1052276; 1131291</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1282843; 1355890</t>
+          <t>1283330; 1355288</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1656559; 1717600</t>
+          <t>1660037; 1721163</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1086380; 1295955</t>
+          <t>1353613; 1435161</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2183172; 2290593</t>
+          <t>2184328; 2287948</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2570398; 2684162</t>
+          <t>2567747; 2683530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3354214; 3448794</t>
+          <t>3354460; 3446916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1959305; 2687620</t>
+          <t>2744018; 2875714</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>386267</t>
+          <t>431481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>372195</t>
+          <t>419772</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>758463</t>
+          <t>851253</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>351067; 396001</t>
+          <t>353469; 397981</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>297588; 340311</t>
+          <t>299643; 344396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395341; 437077</t>
+          <t>395293; 438078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>356766; 410580</t>
+          <t>403393; 459684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>285240; 327157</t>
+          <t>285825; 328329</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>284078; 324293</t>
+          <t>283363; 328308</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>386826; 426866</t>
+          <t>388234; 429164</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>350477; 394719</t>
+          <t>397026; 445712</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>652789; 714166</t>
+          <t>651839; 713252</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>597037; 658482</t>
+          <t>596161; 657700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>794588; 851957</t>
+          <t>799215; 853758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>723192; 794249</t>
+          <t>812872; 889187</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1991359</t>
+          <t>2230116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2118128</t>
+          <t>2389782</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4109486</t>
+          <t>4619899</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2250039; 2355032</t>
+          <t>2246459; 2354550</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2270364; 2376428</t>
+          <t>2270286; 2377566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2697468; 2789583</t>
+          <t>2700113; 2789519</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1460127; 2166149</t>
+          <t>2162014; 2290971</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2385562; 2491086</t>
+          <t>2391150; 2493440</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2595216; 2702607</t>
+          <t>2593910; 2699627</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2917427; 3003380</t>
+          <t>2920575; 3004631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1940528; 2193395</t>
+          <t>2332910; 2442468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4665905; 4815066</t>
+          <t>4670773; 4816316</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4900532; 5052851</t>
+          <t>4903403; 5050165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5641527; 5767447</t>
+          <t>5639553; 5761948</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3604878; 4311230</t>
+          <t>4536736; 4707324</t>
         </is>
       </c>
     </row>
